--- a/Insurance Rate Data Scraper/output/az_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/az_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R180"/>
+  <dimension ref="A1:T180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,6 +707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -957,6 +1007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1047,6 +1107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1132,6 +1202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1222,6 +1302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1312,6 +1402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1402,6 +1502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1492,6 +1602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1574,7 +1694,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1794,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1894,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1994,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2094,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2194,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2294,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2394,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2494,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2594,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2694,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2794,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2894,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2994,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2834,7 +3094,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2924,7 +3194,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3294,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3394,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3494,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3284,7 +3594,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3694,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3794,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3889,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3642,6 +3992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3732,6 +4092,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3822,6 +4192,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3912,6 +4292,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4002,6 +4392,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4092,6 +4492,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4182,6 +4592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4272,6 +4692,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4362,6 +4792,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4452,6 +4892,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4542,6 +4992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4632,6 +5092,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4719,7 +5189,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4809,7 +5289,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4902,6 +5392,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4992,6 +5492,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5082,6 +5592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5172,6 +5692,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5262,6 +5792,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5352,6 +5892,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5442,6 +5992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5532,6 +6092,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5622,6 +6192,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5712,6 +6292,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5802,6 +6392,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5892,6 +6492,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5982,6 +6592,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6072,6 +6692,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6162,6 +6792,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6252,6 +6892,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6342,6 +6992,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6424,7 +7084,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6509,7 +7179,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6602,6 +7282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6692,6 +7382,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6782,6 +7482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6872,6 +7582,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6962,6 +7682,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7052,6 +7782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7142,6 +7882,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7232,6 +7982,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7322,6 +8082,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7412,6 +8182,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7502,6 +8282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7592,6 +8382,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7682,6 +8482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7772,6 +8582,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7862,6 +8682,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7952,6 +8782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8042,6 +8882,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8132,6 +8982,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8222,6 +9082,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -8312,6 +9182,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8402,6 +9282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8489,7 +9379,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8579,7 +9479,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8669,7 +9579,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8759,7 +9679,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8849,7 +9779,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8939,7 +9879,17 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9029,7 +9979,17 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9119,7 +10079,17 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9209,7 +10179,17 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9299,7 +10279,17 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9389,7 +10379,17 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9482,6 +10482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9572,6 +10582,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9659,7 +10679,17 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9749,7 +10779,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9842,6 +10882,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9932,6 +10982,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -10022,6 +11082,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10112,6 +11182,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10202,6 +11282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10292,6 +11382,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10379,7 +11479,17 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10469,7 +11579,17 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10559,7 +11679,17 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10649,7 +11779,17 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10739,7 +11879,17 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10829,7 +11979,17 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10919,7 +12079,17 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11009,7 +12179,17 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11102,6 +12282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11192,6 +12382,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11282,6 +12482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11372,6 +12582,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11462,6 +12682,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11552,6 +12782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11639,7 +12879,17 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11729,7 +12979,17 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11819,7 +13079,17 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11909,7 +13179,17 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11999,7 +13279,17 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12089,7 +13379,17 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12182,6 +13482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12272,6 +13582,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -12362,6 +13682,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -12452,6 +13782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -12542,6 +13882,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12627,6 +13977,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12712,6 +14072,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -12797,6 +14167,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -12872,6 +14252,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -12947,6 +14337,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13027,6 +14427,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13107,6 +14517,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13197,6 +14617,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13287,6 +14717,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13369,7 +14809,17 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13454,7 +14904,17 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13534,7 +14994,17 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13614,7 +15084,17 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13704,7 +15184,17 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13794,7 +15284,17 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13884,7 +15384,17 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -13974,7 +15484,17 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14064,7 +15584,17 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14154,7 +15684,17 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14242,6 +15782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14332,6 +15882,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -14422,6 +15982,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -14512,6 +16082,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -14602,6 +16182,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -14692,6 +16282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -14782,6 +16382,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -14872,6 +16482,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -14962,6 +16582,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -15052,6 +16682,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -15142,6 +16782,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -15232,6 +16882,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -15322,6 +16982,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15409,7 +17079,17 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15499,7 +17179,17 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15589,7 +17279,17 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15679,7 +17379,17 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15769,7 +17479,17 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15859,7 +17579,17 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15944,7 +17674,17 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16034,7 +17774,17 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16124,7 +17874,17 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16214,7 +17974,17 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16304,7 +18074,17 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16394,7 +18174,17 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16484,7 +18274,17 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/az_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/az_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T180"/>
+  <dimension ref="A1:U180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,9 +619,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,9 +720,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,9 +821,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,9 +922,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,9 +1023,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1114,9 +1124,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1209,9 +1220,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1309,9 +1321,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1409,9 +1422,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1509,9 +1523,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1609,9 +1624,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1704,9 +1720,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1794,7 +1811,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1804,7 +1821,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1916,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1904,7 +1926,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2021,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2004,7 +2031,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2126,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2104,7 +2136,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2231,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2204,7 +2241,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2336,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2304,7 +2346,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2441,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2404,7 +2451,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2546,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2504,7 +2556,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2651,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2604,7 +2661,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2704,9 +2766,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2804,9 +2867,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2904,9 +2968,10 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3004,9 +3069,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3104,9 +3170,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3204,9 +3271,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3304,9 +3372,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3404,9 +3473,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3504,9 +3574,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3604,9 +3675,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3704,9 +3776,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3804,9 +3877,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3899,9 +3973,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3999,9 +4074,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4099,9 +4175,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4199,9 +4276,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4299,9 +4377,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4399,9 +4478,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4499,9 +4579,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4599,9 +4680,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4699,9 +4781,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4799,9 +4882,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4899,9 +4983,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4999,9 +5084,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5099,9 +5185,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5189,7 +5276,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5199,7 +5286,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5381,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5299,7 +5391,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -5399,9 +5496,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5499,9 +5597,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5599,9 +5698,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5699,9 +5799,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5799,9 +5900,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5899,9 +6001,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5999,9 +6102,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6099,9 +6203,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6199,9 +6304,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6299,9 +6405,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6399,9 +6506,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6499,9 +6607,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6599,9 +6708,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6699,9 +6809,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6799,9 +6910,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6899,9 +7011,10 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6999,9 +7112,10 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7094,9 +7208,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7189,9 +7304,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7289,9 +7405,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7389,9 +7506,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7489,9 +7607,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7589,9 +7708,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7689,9 +7809,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7789,9 +7910,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7889,9 +8011,10 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7989,9 +8112,10 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8089,9 +8213,10 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8189,9 +8314,10 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8289,9 +8415,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8389,9 +8516,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8489,9 +8617,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8589,9 +8718,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8689,9 +8819,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8789,9 +8920,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8889,9 +9021,10 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8989,9 +9122,10 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9089,9 +9223,10 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9189,9 +9324,10 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9289,9 +9425,10 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9389,9 +9526,10 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9489,9 +9627,10 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9589,9 +9728,10 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9689,9 +9829,10 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9789,9 +9930,10 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9889,9 +10031,10 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9989,9 +10132,10 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10089,9 +10233,10 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10189,9 +10334,10 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10289,9 +10435,10 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10389,9 +10536,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10489,9 +10637,10 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10589,9 +10738,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10679,7 +10829,7 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -10689,7 +10839,12 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -10789,9 +10944,10 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10889,9 +11045,10 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10989,9 +11146,10 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11089,9 +11247,10 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11189,9 +11348,10 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11289,9 +11449,10 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11389,9 +11550,10 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11479,7 +11641,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -11489,7 +11651,12 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -11579,7 +11746,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -11589,7 +11756,12 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -11689,9 +11861,10 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11789,9 +11962,10 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11889,9 +12063,10 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11989,9 +12164,10 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12089,9 +12265,10 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12189,9 +12366,10 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12289,9 +12467,10 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12389,9 +12568,10 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12489,9 +12669,10 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12589,9 +12770,10 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12689,9 +12871,10 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12789,9 +12972,10 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12889,9 +13073,10 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12979,7 +13164,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -12989,7 +13174,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -13079,7 +13269,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -13089,7 +13279,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -13189,9 +13384,10 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13289,9 +13485,10 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13389,9 +13586,10 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13489,9 +13687,10 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13589,9 +13788,10 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13689,9 +13889,10 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13789,9 +13990,10 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13889,9 +14091,10 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13984,9 +14187,10 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14079,9 +14283,10 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14174,9 +14379,10 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14259,9 +14465,10 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14344,9 +14551,10 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14434,9 +14642,10 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14524,9 +14733,10 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14624,9 +14834,10 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14724,9 +14935,10 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14819,9 +15031,10 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14914,9 +15127,10 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15004,9 +15218,10 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15094,9 +15309,10 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15184,7 +15400,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
@@ -15194,7 +15410,12 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15505,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
@@ -15294,7 +15515,12 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -15384,7 +15610,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -15394,7 +15620,12 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -15484,7 +15715,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -15494,7 +15725,12 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -15594,9 +15830,10 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15694,9 +15931,10 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15789,9 +16027,10 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15889,9 +16128,10 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15989,9 +16229,10 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16089,9 +16330,10 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16189,9 +16431,10 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16289,9 +16532,10 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16389,9 +16633,10 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16489,9 +16734,10 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16589,9 +16835,10 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16689,9 +16936,10 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16789,9 +17037,10 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16889,9 +17138,10 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -16989,9 +17239,10 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17079,7 +17330,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S168" t="inlineStr">
@@ -17089,7 +17340,12 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17435,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S169" t="inlineStr">
@@ -17189,7 +17445,12 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17540,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
@@ -17289,7 +17550,12 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -17379,7 +17645,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
@@ -17389,7 +17655,12 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17750,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -17489,7 +17760,12 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>date_relaxed</t>
         </is>
       </c>
     </row>
@@ -17579,7 +17855,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
@@ -17589,7 +17865,12 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -17684,9 +17965,10 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -17774,7 +18056,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
@@ -17784,7 +18066,12 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -17874,7 +18161,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
@@ -17884,7 +18171,12 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -17974,7 +18266,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -17984,7 +18276,12 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -18084,9 +18381,10 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18184,9 +18482,10 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18284,9 +18583,10 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/az_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/az_final_rates.xlsx
@@ -1710,7 +1710,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1720,10 +1720,14 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15021,7 +15025,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
@@ -15031,10 +15035,14 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15117,7 +15125,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S146" t="inlineStr">
@@ -15127,10 +15135,14 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17955,7 +17967,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
@@ -17965,10 +17977,14 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/az_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/az_final_rates.xlsx
@@ -15220,7 +15220,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -15230,10 +15230,14 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U147" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15311,7 +15315,7 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
@@ -15321,10 +15325,14 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr"/>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">

--- a/Insurance Rate Data Scraper/output/az_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/az_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U196"/>
+  <dimension ref="A1:U231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20087,6 +20087,3341 @@
         </is>
       </c>
       <c r="U196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>54642</v>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>111401256</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>33.100%</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-50.200%</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>SFMA-134876219</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134876219/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>1185176</v>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>1500437436</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>33.700%</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-65.400%</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>SFMA-134876219</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134876219/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-102059</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>67246</v>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>129807679</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-5.900%</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>SFMA-134951991</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134951991/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>06/01/2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-922725</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1404576</v>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>1565501138</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>1.700%</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-9.400%</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>SFMA-134951991</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134951991/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>26.700%</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>51407769</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>429281</v>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>519806566</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>75.200%</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>SFMA-134941974</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134941974/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>52053</v>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>89475487</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>16.000%</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>-14.100%</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GECC-134942935</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134942935/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>06/11/2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>19999</v>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>33400020</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>24.100%</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-18.600%</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>GECC-134942935</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134942935/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>04/24/2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Progressive Advanced Insurance Company</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>5.500%</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>5562440</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>476780</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>570313365</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>4.800%</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-4.100%</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>PRGS-134918992</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134918992/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>04/24/2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Progressive Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-1.100%</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-1.000%</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-3990785</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>270327</v>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>398545905</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>PRGS-134918992</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134918992/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>342360209</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>ALSE-134916333</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134916333/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>08/18/2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>52372</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>147259381</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>12.000%</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-12.000%</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ALSE-135013662</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135013662/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>06/26/2026</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>51803</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>141001824</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>10.400%</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-5.900%</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>TRVD-G134965697</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134978416/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>5028</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>LBPM-135013384</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135013384/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>08/17/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Liberty Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>7010983</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>LBPM-135013384</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135013384/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>08/29/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>13.000%</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>835515</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>9814</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>27985861</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>40.000%</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-7.000%</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>LBPM-135001710</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135001710/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>07/18/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>11253</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>5596942</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>LBPM-134969366</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134969366/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>03/30/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Company of Arizona</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>11.100%</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-0.300%</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-112000</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>22429</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>38491000</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-10.560%</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>FARM-134912916</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134912916/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Nationwide Affinity Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1259</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>3321717</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>1.900%</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-0.700%</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>NWPP-G135007530</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135015381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Nationwide General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>9127</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>22091346</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>21.900%</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-31.000%</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>NWPP-G135007530</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135015381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>08/10/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Nationwide Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-23</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1859</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>5015762</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>0.800%</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-0.800%</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>NWPP-G135007530</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135015381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>06/25/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Nationwide General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-8.000%</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-467218</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>1862</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>5824617</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>16.500%</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-30.900%</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>NWPP-G134957656</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134960974/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-4.100%</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-5745546</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>61503</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>191607615</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>476.010%</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-72.550%</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>AMFC-135023474</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135023474/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-5.628%</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-292175</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>1166</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>5191522</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-19.000%</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>CFPC-134908354</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908354/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-5.259%</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-1436109</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>7305</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>27309589</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>11.500%</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-19.900%</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>CFPC-134908354</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908354/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-5.761%</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-23174</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>101</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>402243</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>3.600%</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-18.900%</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>CFPC-134908354</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908354/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-8.647%</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-5582</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>43</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>64557</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>11.300%</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-26.700%</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>CFPC-134908392</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908392/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-7.136%</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-23145</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>227</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>324353</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>16.600%</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-32.900%</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>CFPC-134908392</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908392/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-9.611%</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-349</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>5</v>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>1.100%</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-19.500%</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>CFPC-134908392</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908392/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-13.108%</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-13365</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>125</v>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>101954</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>0.900%</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>-39.300%</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>CFPC-134908419</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908419/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-11.259%</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-48797</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>735</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>433409</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>8.700%</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-39.800%</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>CFPC-134908419</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908419/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-14.680%</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-1322</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>7</v>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-22.300%</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>CFPC-134908419</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908419/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>COUNTRY Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-8.414%</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>-9020</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>150</v>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>107196</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>18.400%</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-20.000%</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>CFPC-134908421</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908421/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-7.776%</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>-48575</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>1052</v>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>624691</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>19.000%</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-20.000%</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>CFPC-134908421</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908421/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>COUNTRY Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-5.619%</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-2.083%</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-312</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>9</v>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>14968</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>2.600%</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-11.100%</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>CFPC-134908421</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/134908421/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>15.600%</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>367703</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>10543</v>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>14422318</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GNSC-135021048</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Acknowledged</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>output/pdfs/AZ/135021048/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
